--- a/downloads/AeroSafe_Questionnaire_Summary_Table.xlsx
+++ b/downloads/AeroSafe_Questionnaire_Summary_Table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/albertopetrucci/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/albertopetrucci/Documents/github/aerosafe/downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5A101B-8AFD-E742-B8FC-E25E1AEE8AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82005C5-E0F1-8D4B-B15D-470BD96E738F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,9 +93,6 @@
     <t>Other</t>
   </si>
   <si>
-    <t>Thales Alenia Space</t>
-  </si>
-  <si>
     <t>Experience with AI/ML systems</t>
   </si>
   <si>
@@ -305,6 +302,9 @@
   </si>
   <si>
     <t>Absolute Mean</t>
+  </si>
+  <si>
+    <t>Space Company</t>
   </si>
 </sst>
 </file>
@@ -496,6 +496,27 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -530,27 +551,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -856,72 +856,72 @@
   <sheetData>
     <row r="1" spans="1:13" ht="14" x14ac:dyDescent="0.15">
       <c r="A1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="14" x14ac:dyDescent="0.15">
+      <c r="A2" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="14" x14ac:dyDescent="0.15">
-      <c r="A2" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="C2" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="19"/>
@@ -929,30 +929,30 @@
       <c r="M2" s="9"/>
     </row>
     <row r="3" spans="1:13" ht="14" x14ac:dyDescent="0.15">
-      <c r="A3" s="35"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="I3" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J3" s="9">
         <f>AVERAGE(VLOOKUP(D3,Values!$A$2:$B$4,2,0),VLOOKUP(E3,Values!$A$2:$B$4,2,0),VLOOKUP(F3,Values!$A$2:$B$4,2,0),VLOOKUP(G3,Values!$A$2:$B$4,2,0),VLOOKUP(H3,Values!$A$2:$B$4,2,0),VLOOKUP(I3,Values!$A$2:$B$4,2,0))</f>
@@ -966,30 +966,30 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:13" ht="14" x14ac:dyDescent="0.15">
-      <c r="A4" s="35"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="H4" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J4" s="9">
         <f>AVERAGE(VLOOKUP(D4,Values!$A$2:$B$4,2,0),VLOOKUP(E4,Values!$A$2:$B$4,2,0),VLOOKUP(F4,Values!$A$2:$B$4,2,0),VLOOKUP(G4,Values!$A$2:$B$4,2,0),VLOOKUP(H4,Values!$A$2:$B$4,2,0),VLOOKUP(I4,Values!$A$2:$B$4,2,0))</f>
@@ -1003,30 +1003,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:13" ht="14" x14ac:dyDescent="0.15">
-      <c r="A5" s="35"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>20</v>
-      </c>
       <c r="F5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J5" s="9">
         <f>AVERAGE(VLOOKUP(D5,Values!$A$2:$B$4,2,0),VLOOKUP(E5,Values!$A$2:$B$4,2,0),VLOOKUP(F5,Values!$A$2:$B$4,2,0),VLOOKUP(G5,Values!$A$2:$B$4,2,0),VLOOKUP(H5,Values!$A$2:$B$4,2,0),VLOOKUP(I5,Values!$A$2:$B$4,2,0))</f>
@@ -1040,30 +1040,30 @@
       <c r="M5" s="9"/>
     </row>
     <row r="6" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A6" s="35"/>
+      <c r="A6" s="24"/>
       <c r="B6" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="19"/>
@@ -1071,9 +1071,9 @@
       <c r="M6" s="9"/>
     </row>
     <row r="7" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A7" s="36"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>16</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="8" spans="1:13" ht="42" x14ac:dyDescent="0.15">
       <c r="A8" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>13</v>
@@ -1123,7 +1123,7 @@
         <f t="shared" ref="J8:J29" si="0">AVERAGE(D8:I8)</f>
         <v>4</v>
       </c>
-      <c r="K8" s="40">
+      <c r="K8" s="22">
         <f>AVERAGE(J8:J9)</f>
         <v>4.25</v>
       </c>
@@ -1138,13 +1138,13 @@
     </row>
     <row r="9" spans="1:13" ht="42" x14ac:dyDescent="0.15">
       <c r="A9" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="8">
         <v>4</v>
@@ -1168,7 +1168,7 @@
         <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
-      <c r="K9" s="40"/>
+      <c r="K9" s="22"/>
       <c r="L9" s="9">
         <f>STDEV(D9:I9)</f>
         <v>0.83666002653407556</v>
@@ -1180,13 +1180,13 @@
     </row>
     <row r="10" spans="1:13" ht="28" x14ac:dyDescent="0.15">
       <c r="A10" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="13">
         <v>4</v>
@@ -1224,11 +1224,11 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="42" x14ac:dyDescent="0.15">
-      <c r="A11" s="34" t="s">
-        <v>39</v>
+      <c r="A11" s="23" t="s">
+        <v>38</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>12</v>
@@ -1255,23 +1255,23 @@
         <f t="shared" si="0"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="K11" s="22">
+      <c r="K11" s="29">
         <f>AVERAGE(J11:J13)</f>
         <v>4.2222222222222223</v>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="35">
         <f>STDEV(D11:I13)</f>
         <v>0.73208449814095855</v>
       </c>
-      <c r="M11" s="28">
+      <c r="M11" s="35">
         <f>QUARTILE(E11:J13,3)-QUARTILE(E11:J13,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="42" x14ac:dyDescent="0.15">
-      <c r="A12" s="35"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>11</v>
@@ -1298,17 +1298,17 @@
         <f t="shared" si="0"/>
         <v>3.8333333333333335</v>
       </c>
-      <c r="K12" s="23"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
     </row>
     <row r="13" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A13" s="36"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" s="8">
         <v>4</v>
@@ -1332,16 +1332,16 @@
         <f t="shared" si="0"/>
         <v>4.166666666666667</v>
       </c>
-      <c r="K13" s="24"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
     </row>
     <row r="14" spans="1:13" ht="42" x14ac:dyDescent="0.15">
-      <c r="A14" s="37" t="s">
-        <v>40</v>
+      <c r="A14" s="26" t="s">
+        <v>39</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>10</v>
@@ -1368,23 +1368,23 @@
         <f t="shared" si="0"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="32">
         <f>AVERAGE(J14:J16)</f>
         <v>4.7777777777777777</v>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="38">
         <f>STDEV(D14:I16)</f>
         <v>0.42779263194649864</v>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="38">
         <f>QUARTILE(E14:J16,3)-QUARTILE(E14:J16,1)</f>
         <v>0.16666666666666696</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="42" x14ac:dyDescent="0.15">
-      <c r="A15" s="38"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>9</v>
@@ -1411,14 +1411,14 @@
         <f t="shared" si="0"/>
         <v>4.833333333333333</v>
       </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
     </row>
     <row r="16" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A16" s="39"/>
+      <c r="A16" s="28"/>
       <c r="B16" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>8</v>
@@ -1445,19 +1445,19 @@
         <f t="shared" si="0"/>
         <v>4.833333333333333</v>
       </c>
-      <c r="K16" s="27"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
     </row>
     <row r="17" spans="1:13" ht="42" x14ac:dyDescent="0.15">
-      <c r="A17" s="34" t="s">
-        <v>41</v>
+      <c r="A17" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" s="8">
         <v>4</v>
@@ -1481,26 +1481,26 @@
         <f t="shared" si="0"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="K17" s="22">
+      <c r="K17" s="29">
         <f>AVERAGE(J17:J23)</f>
         <v>4.4761904761904763</v>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="35">
         <f>STDEV(D17:I23)</f>
         <v>0.74040513755103221</v>
       </c>
-      <c r="M17" s="28">
+      <c r="M17" s="35">
         <f>QUARTILE(E17:J23,3)-QUARTILE(E17:J23,1)</f>
         <v>0.66666666666666696</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="42" x14ac:dyDescent="0.15">
-      <c r="A18" s="35"/>
+      <c r="A18" s="24"/>
       <c r="B18" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" s="8">
         <v>4</v>
@@ -1524,14 +1524,14 @@
         <f t="shared" si="0"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="K18" s="23"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
     </row>
     <row r="19" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A19" s="35"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>7</v>
@@ -1558,14 +1558,14 @@
         <f t="shared" si="0"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="K19" s="23"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
     </row>
     <row r="20" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A20" s="35"/>
+      <c r="A20" s="24"/>
       <c r="B20" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>6</v>
@@ -1592,14 +1592,14 @@
         <f t="shared" si="0"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="K20" s="23"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13" ht="70" x14ac:dyDescent="0.15">
-      <c r="A21" s="35"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>5</v>
@@ -1626,17 +1626,17 @@
         <f t="shared" si="0"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="K21" s="23"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" ht="42" x14ac:dyDescent="0.15">
-      <c r="A22" s="35"/>
+      <c r="A22" s="24"/>
       <c r="B22" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" s="8">
         <v>3</v>
@@ -1660,17 +1660,17 @@
         <f t="shared" si="0"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="K22" s="23"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A23" s="36"/>
+      <c r="A23" s="25"/>
       <c r="B23" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" s="8">
         <v>3</v>
@@ -1694,16 +1694,16 @@
         <f t="shared" si="0"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="K23" s="24"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
     </row>
     <row r="24" spans="1:13" ht="56" x14ac:dyDescent="0.15">
       <c r="A24" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>4</v>
@@ -1744,11 +1744,11 @@
       </c>
     </row>
     <row r="25" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A25" s="34" t="s">
-        <v>42</v>
+      <c r="A25" s="23" t="s">
+        <v>41</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>3</v>
@@ -1775,23 +1775,23 @@
         <f t="shared" si="0"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="K25" s="22">
+      <c r="K25" s="29">
         <f>AVERAGE(J25:J29)</f>
         <v>4.5333333333333332</v>
       </c>
-      <c r="L25" s="28">
+      <c r="L25" s="35">
         <f>STDEV(D25:I29)</f>
         <v>0.73029674334022221</v>
       </c>
-      <c r="M25" s="28">
+      <c r="M25" s="35">
         <f>QUARTILE(E25:J29,3)-QUARTILE(E25:J29,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A26" s="35"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>2</v>
@@ -1818,14 +1818,14 @@
         <f t="shared" si="0"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="K26" s="23"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
     </row>
     <row r="27" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A27" s="35"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>1</v>
@@ -1852,14 +1852,14 @@
         <f t="shared" si="0"/>
         <v>4.833333333333333</v>
       </c>
-      <c r="K27" s="23"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
     </row>
     <row r="28" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A28" s="35"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>0</v>
@@ -1886,17 +1886,17 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K28" s="23"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
     </row>
     <row r="29" spans="1:13" ht="28" x14ac:dyDescent="0.15">
-      <c r="A29" s="36"/>
+      <c r="A29" s="25"/>
       <c r="B29" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D29" s="8">
         <v>5</v>
@@ -1920,31 +1920,31 @@
         <f t="shared" si="0"/>
         <v>4.166666666666667</v>
       </c>
-      <c r="K29" s="24"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="37"/>
+      <c r="M29" s="37"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M29" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="18">
+    <mergeCell ref="L11:L13"/>
+    <mergeCell ref="M11:M13"/>
+    <mergeCell ref="L25:L29"/>
+    <mergeCell ref="M25:M29"/>
+    <mergeCell ref="L17:L23"/>
+    <mergeCell ref="M17:M23"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="M14:M16"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="K14:K16"/>
+    <mergeCell ref="K17:K23"/>
+    <mergeCell ref="K25:K29"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A17:A23"/>
-    <mergeCell ref="A25:A29"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="K14:K16"/>
-    <mergeCell ref="K17:K23"/>
-    <mergeCell ref="K25:K29"/>
-    <mergeCell ref="M25:M29"/>
-    <mergeCell ref="L17:L23"/>
-    <mergeCell ref="M17:M23"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M14:M16"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="M11:M13"/>
-    <mergeCell ref="L25:L29"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D8:I29">
@@ -1968,15 +1968,15 @@
   <sheetData>
     <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1">
         <f>(0+2)/2</f>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1">
         <f>(3+5)/2</f>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>16</v>
